--- a/app/templates_excel/albedo/a7_nodes_en.xlsx
+++ b/app/templates_excel/albedo/a7_nodes_en.xlsx
@@ -1184,10 +1184,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>A window at an open grave.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>A bridge being built across a gorge.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1444,10 +1440,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Chinese woman nusing a baby with a message.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>One hand slightly flexed with a very prominent thumb.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1572,10 +1564,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>A pagent.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Sunshine just after a storm.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2336,10 +2324,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>A tree feiled and sawed.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Butterfly emerging from a chrysalis.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2416,10 +2400,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>A gigatic tent.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>A master instructing his pupil.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2440,10 +2420,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>An inhibited island.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>The purging of the priesthood.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2605,6 +2581,30 @@
   </si>
   <si>
     <t>A professor peering over his glasses.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A gigantic tent.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A tree felled and sawed.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Chinese woman nursing a baby with a message.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A widow at an open grave.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A pageant.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>An inhabited island.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -10226,7 +10226,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="15" x14ac:dyDescent="0.3">
       <c r="A1" s="12" t="s">
-        <v>700</v>
+        <v>694</v>
       </c>
       <c r="B1" s="12"/>
       <c r="C1" s="12"/>
@@ -10240,46 +10240,46 @@
     </row>
     <row r="4" spans="1:10" ht="15" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>701</v>
+        <v>695</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="15" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>702</v>
+        <v>696</v>
       </c>
     </row>
     <row r="8" spans="1:10" s="5" customFormat="1" ht="15" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
+        <v>697</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>698</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>699</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>700</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>701</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>702</v>
+      </c>
+      <c r="G8" s="5" t="s">
         <v>703</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="H8" s="5" t="s">
         <v>704</v>
       </c>
-      <c r="C8" s="5" t="s">
-        <v>705</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>706</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>707</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>708</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>709</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>710</v>
-      </c>
       <c r="I8" s="5" t="s">
-        <v>699</v>
+        <v>693</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="15" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
-        <v>711</v>
+        <v>705</v>
       </c>
       <c r="I9" s="7" t="s">
         <v>344</v>
@@ -10287,7 +10287,7 @@
     </row>
     <row r="10" spans="1:10" ht="15" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="I10" s="7" t="s">
         <v>345</v>
@@ -10519,30 +10519,30 @@
     </row>
     <row r="39" spans="1:9" s="8" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B39" s="8" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="F39" s="8" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="H39" s="8" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A40" s="9" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="I40" s="7" t="s">
         <v>374</v>
@@ -10550,7 +10550,7 @@
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A41" s="9" t="s">
-        <v>714</v>
+        <v>708</v>
       </c>
       <c r="I41" s="7" t="s">
         <v>375</v>
@@ -10577,7 +10577,7 @@
         <v>30</v>
       </c>
       <c r="I44" s="7" t="s">
-        <v>378</v>
+        <v>731</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.4">
@@ -10585,7 +10585,7 @@
         <v>31</v>
       </c>
       <c r="I45" s="7" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.4">
@@ -10593,7 +10593,7 @@
         <v>32</v>
       </c>
       <c r="I46" s="7" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.4">
@@ -10601,7 +10601,7 @@
         <v>33</v>
       </c>
       <c r="I47" s="7" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.4">
@@ -10609,7 +10609,7 @@
         <v>34</v>
       </c>
       <c r="I48" s="7" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.4">
@@ -10617,7 +10617,7 @@
         <v>35</v>
       </c>
       <c r="I49" s="7" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.4">
@@ -10625,7 +10625,7 @@
         <v>36</v>
       </c>
       <c r="I50" s="7" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.4">
@@ -10633,7 +10633,7 @@
         <v>37</v>
       </c>
       <c r="I51" s="7" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.4">
@@ -10641,7 +10641,7 @@
         <v>38</v>
       </c>
       <c r="I52" s="7" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.4">
@@ -10649,7 +10649,7 @@
         <v>39</v>
       </c>
       <c r="I53" s="7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.4">
@@ -10657,7 +10657,7 @@
         <v>40</v>
       </c>
       <c r="I54" s="7" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.4">
@@ -10665,7 +10665,7 @@
         <v>41</v>
       </c>
       <c r="I55" s="7" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.4">
@@ -10673,7 +10673,7 @@
         <v>42</v>
       </c>
       <c r="I56" s="7" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.4">
@@ -10681,7 +10681,7 @@
         <v>43</v>
       </c>
       <c r="I57" s="7" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.4">
@@ -10689,7 +10689,7 @@
         <v>44</v>
       </c>
       <c r="I58" s="7" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.4">
@@ -10697,7 +10697,7 @@
         <v>45</v>
       </c>
       <c r="I59" s="7" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.4">
@@ -10705,7 +10705,7 @@
         <v>46</v>
       </c>
       <c r="I60" s="7" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.4">
@@ -10713,7 +10713,7 @@
         <v>47</v>
       </c>
       <c r="I61" s="7" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.4">
@@ -10721,7 +10721,7 @@
         <v>48</v>
       </c>
       <c r="I62" s="7" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.4">
@@ -10729,7 +10729,7 @@
         <v>49</v>
       </c>
       <c r="I63" s="7" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.4">
@@ -10737,7 +10737,7 @@
         <v>50</v>
       </c>
       <c r="I64" s="7" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.4">
@@ -10745,7 +10745,7 @@
         <v>51</v>
       </c>
       <c r="I65" s="7" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.4">
@@ -10753,7 +10753,7 @@
         <v>52</v>
       </c>
       <c r="I66" s="7" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.4">
@@ -10761,7 +10761,7 @@
         <v>53</v>
       </c>
       <c r="I67" s="7" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.4">
@@ -10769,7 +10769,7 @@
         <v>54</v>
       </c>
       <c r="I68" s="7" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.4">
@@ -10777,46 +10777,46 @@
         <v>55</v>
       </c>
       <c r="I69" s="7" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="70" spans="1:9" s="8" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B70" s="8" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="C70" s="8" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="D70" s="8" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="E70" s="8" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="F70" s="8" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="G70" s="8" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="H70" s="8" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A71" s="10" t="s">
-        <v>715</v>
+        <v>709</v>
       </c>
       <c r="I71" s="7" t="s">
-        <v>729</v>
+        <v>723</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A72" s="10" t="s">
-        <v>716</v>
+        <v>710</v>
       </c>
       <c r="I72" s="7" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.4">
@@ -10824,7 +10824,7 @@
         <v>56</v>
       </c>
       <c r="I73" s="7" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.4">
@@ -10832,7 +10832,7 @@
         <v>57</v>
       </c>
       <c r="I74" s="7" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.4">
@@ -10840,7 +10840,7 @@
         <v>58</v>
       </c>
       <c r="I75" s="7" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.4">
@@ -10848,7 +10848,7 @@
         <v>59</v>
       </c>
       <c r="I76" s="7" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.4">
@@ -10856,7 +10856,7 @@
         <v>60</v>
       </c>
       <c r="I77" s="7" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.4">
@@ -10864,7 +10864,7 @@
         <v>61</v>
       </c>
       <c r="I78" s="7" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.4">
@@ -10872,7 +10872,7 @@
         <v>62</v>
       </c>
       <c r="I79" s="7" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.4">
@@ -10880,7 +10880,7 @@
         <v>63</v>
       </c>
       <c r="I80" s="7" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.4">
@@ -10888,7 +10888,7 @@
         <v>64</v>
       </c>
       <c r="I81" s="7" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.4">
@@ -10896,7 +10896,7 @@
         <v>65</v>
       </c>
       <c r="I82" s="7" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.4">
@@ -10904,7 +10904,7 @@
         <v>66</v>
       </c>
       <c r="I83" s="7" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.4">
@@ -10912,7 +10912,7 @@
         <v>67</v>
       </c>
       <c r="I84" s="7" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.4">
@@ -10920,7 +10920,7 @@
         <v>68</v>
       </c>
       <c r="I85" s="7" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.4">
@@ -10928,7 +10928,7 @@
         <v>69</v>
       </c>
       <c r="I86" s="7" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.4">
@@ -10936,7 +10936,7 @@
         <v>70</v>
       </c>
       <c r="I87" s="7" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.4">
@@ -10944,7 +10944,7 @@
         <v>71</v>
       </c>
       <c r="I88" s="7" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.4">
@@ -10952,7 +10952,7 @@
         <v>72</v>
       </c>
       <c r="I89" s="7" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.4">
@@ -10960,7 +10960,7 @@
         <v>73</v>
       </c>
       <c r="I90" s="7" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.4">
@@ -10968,7 +10968,7 @@
         <v>74</v>
       </c>
       <c r="I91" s="7" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.4">
@@ -10976,7 +10976,7 @@
         <v>75</v>
       </c>
       <c r="I92" s="7" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.4">
@@ -10984,7 +10984,7 @@
         <v>76</v>
       </c>
       <c r="I93" s="7" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.4">
@@ -10992,7 +10992,7 @@
         <v>77</v>
       </c>
       <c r="I94" s="7" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.4">
@@ -11000,7 +11000,7 @@
         <v>78</v>
       </c>
       <c r="I95" s="7" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.4">
@@ -11008,7 +11008,7 @@
         <v>79</v>
       </c>
       <c r="I96" s="7" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.4">
@@ -11016,7 +11016,7 @@
         <v>80</v>
       </c>
       <c r="I97" s="7" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.4">
@@ -11024,7 +11024,7 @@
         <v>81</v>
       </c>
       <c r="I98" s="7" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.4">
@@ -11032,7 +11032,7 @@
         <v>82</v>
       </c>
       <c r="I99" s="7" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.4">
@@ -11040,38 +11040,38 @@
         <v>83</v>
       </c>
       <c r="I100" s="7" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="101" spans="1:9" s="8" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B101" s="8" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="C101" s="8" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="D101" s="8" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="E101" s="8" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="F101" s="8" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="G101" s="8" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="H101" s="8" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A102" s="11" t="s">
-        <v>717</v>
+        <v>711</v>
       </c>
       <c r="I102" s="7" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.4">
@@ -11079,7 +11079,7 @@
         <v>84</v>
       </c>
       <c r="I103" s="7" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.4">
@@ -11087,7 +11087,7 @@
         <v>85</v>
       </c>
       <c r="I104" s="7" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.4">
@@ -11095,7 +11095,7 @@
         <v>86</v>
       </c>
       <c r="I105" s="7" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.4">
@@ -11103,7 +11103,7 @@
         <v>87</v>
       </c>
       <c r="I106" s="7" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.4">
@@ -11111,7 +11111,7 @@
         <v>88</v>
       </c>
       <c r="I107" s="7" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.4">
@@ -11119,7 +11119,7 @@
         <v>89</v>
       </c>
       <c r="I108" s="7" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.4">
@@ -11127,7 +11127,7 @@
         <v>90</v>
       </c>
       <c r="I109" s="7" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.4">
@@ -11135,7 +11135,7 @@
         <v>91</v>
       </c>
       <c r="I110" s="7" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.4">
@@ -11143,7 +11143,7 @@
         <v>92</v>
       </c>
       <c r="I111" s="7" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.4">
@@ -11151,7 +11151,7 @@
         <v>93</v>
       </c>
       <c r="I112" s="7" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.4">
@@ -11159,7 +11159,7 @@
         <v>94</v>
       </c>
       <c r="I113" s="7" t="s">
-        <v>443</v>
+        <v>730</v>
       </c>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.4">
@@ -11167,7 +11167,7 @@
         <v>95</v>
       </c>
       <c r="I114" s="7" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.4">
@@ -11175,7 +11175,7 @@
         <v>96</v>
       </c>
       <c r="I115" s="7" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.4">
@@ -11183,7 +11183,7 @@
         <v>97</v>
       </c>
       <c r="I116" s="7" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.4">
@@ -11191,7 +11191,7 @@
         <v>98</v>
       </c>
       <c r="I117" s="7" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.4">
@@ -11199,7 +11199,7 @@
         <v>99</v>
       </c>
       <c r="I118" s="7" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.4">
@@ -11207,7 +11207,7 @@
         <v>100</v>
       </c>
       <c r="I119" s="7" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.4">
@@ -11215,7 +11215,7 @@
         <v>101</v>
       </c>
       <c r="I120" s="7" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.4">
@@ -11223,7 +11223,7 @@
         <v>102</v>
       </c>
       <c r="I121" s="7" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.4">
@@ -11231,7 +11231,7 @@
         <v>103</v>
       </c>
       <c r="I122" s="7" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.4">
@@ -11239,7 +11239,7 @@
         <v>104</v>
       </c>
       <c r="I123" s="7" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.4">
@@ -11247,7 +11247,7 @@
         <v>105</v>
       </c>
       <c r="I124" s="7" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.4">
@@ -11255,7 +11255,7 @@
         <v>106</v>
       </c>
       <c r="I125" s="7" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.4">
@@ -11263,7 +11263,7 @@
         <v>107</v>
       </c>
       <c r="I126" s="7" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.4">
@@ -11271,7 +11271,7 @@
         <v>108</v>
       </c>
       <c r="I127" s="7" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.4">
@@ -11279,7 +11279,7 @@
         <v>109</v>
       </c>
       <c r="I128" s="7" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.4">
@@ -11287,7 +11287,7 @@
         <v>110</v>
       </c>
       <c r="I129" s="7" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.4">
@@ -11295,7 +11295,7 @@
         <v>111</v>
       </c>
       <c r="I130" s="7" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.4">
@@ -11303,38 +11303,38 @@
         <v>112</v>
       </c>
       <c r="I131" s="7" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
     </row>
     <row r="132" spans="1:9" s="8" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B132" s="8" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="C132" s="8" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="D132" s="8" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="E132" s="8" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="F132" s="8" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="G132" s="8" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="H132" s="8" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A133" s="6" t="s">
-        <v>718</v>
+        <v>712</v>
       </c>
       <c r="I133" s="7" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.4">
@@ -11342,7 +11342,7 @@
         <v>113</v>
       </c>
       <c r="I134" s="7" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.4">
@@ -11350,7 +11350,7 @@
         <v>114</v>
       </c>
       <c r="I135" s="7" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.4">
@@ -11358,7 +11358,7 @@
         <v>115</v>
       </c>
       <c r="I136" s="7" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.4">
@@ -11366,7 +11366,7 @@
         <v>116</v>
       </c>
       <c r="I137" s="7" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.4">
@@ -11374,7 +11374,7 @@
         <v>117</v>
       </c>
       <c r="I138" s="7" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.4">
@@ -11382,7 +11382,7 @@
         <v>118</v>
       </c>
       <c r="I139" s="7" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.4">
@@ -11390,7 +11390,7 @@
         <v>119</v>
       </c>
       <c r="I140" s="7" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.4">
@@ -11398,7 +11398,7 @@
         <v>120</v>
       </c>
       <c r="I141" s="7" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.4">
@@ -11406,7 +11406,7 @@
         <v>121</v>
       </c>
       <c r="I142" s="7" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.4">
@@ -11414,7 +11414,7 @@
         <v>122</v>
       </c>
       <c r="I143" s="7" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.4">
@@ -11422,7 +11422,7 @@
         <v>123</v>
       </c>
       <c r="I144" s="7" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.4">
@@ -11430,7 +11430,7 @@
         <v>124</v>
       </c>
       <c r="I145" s="7" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.4">
@@ -11438,7 +11438,7 @@
         <v>125</v>
       </c>
       <c r="I146" s="7" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.4">
@@ -11446,7 +11446,7 @@
         <v>126</v>
       </c>
       <c r="I147" s="7" t="s">
-        <v>475</v>
+        <v>732</v>
       </c>
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.4">
@@ -11454,7 +11454,7 @@
         <v>127</v>
       </c>
       <c r="I148" s="7" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.4">
@@ -11462,7 +11462,7 @@
         <v>128</v>
       </c>
       <c r="I149" s="7" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.4">
@@ -11470,7 +11470,7 @@
         <v>129</v>
       </c>
       <c r="I150" s="7" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.4">
@@ -11478,7 +11478,7 @@
         <v>130</v>
       </c>
       <c r="I151" s="7" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.4">
@@ -11486,7 +11486,7 @@
         <v>131</v>
       </c>
       <c r="I152" s="7" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.4">
@@ -11494,7 +11494,7 @@
         <v>132</v>
       </c>
       <c r="I153" s="7" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.4">
@@ -11502,7 +11502,7 @@
         <v>133</v>
       </c>
       <c r="I154" s="7" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.4">
@@ -11510,7 +11510,7 @@
         <v>134</v>
       </c>
       <c r="I155" s="7" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.4">
@@ -11518,7 +11518,7 @@
         <v>135</v>
       </c>
       <c r="I156" s="7" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.4">
@@ -11526,7 +11526,7 @@
         <v>136</v>
       </c>
       <c r="I157" s="7" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
     </row>
     <row r="158" spans="1:9" x14ac:dyDescent="0.4">
@@ -11534,7 +11534,7 @@
         <v>137</v>
       </c>
       <c r="I158" s="7" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
     </row>
     <row r="159" spans="1:9" x14ac:dyDescent="0.4">
@@ -11542,7 +11542,7 @@
         <v>138</v>
       </c>
       <c r="I159" s="7" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.4">
@@ -11550,7 +11550,7 @@
         <v>139</v>
       </c>
       <c r="I160" s="7" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
     </row>
     <row r="161" spans="1:9" x14ac:dyDescent="0.4">
@@ -11558,7 +11558,7 @@
         <v>140</v>
       </c>
       <c r="I161" s="7" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
     </row>
     <row r="162" spans="1:9" x14ac:dyDescent="0.4">
@@ -11566,46 +11566,46 @@
         <v>141</v>
       </c>
       <c r="I162" s="7" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
     </row>
     <row r="163" spans="1:9" s="8" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B163" s="8" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="C163" s="8" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="D163" s="8" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="E163" s="8" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="F163" s="8" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="G163" s="8" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="H163" s="8" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
     </row>
     <row r="164" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A164" s="9" t="s">
-        <v>719</v>
+        <v>713</v>
       </c>
       <c r="I164" s="7" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
     </row>
     <row r="165" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A165" s="9" t="s">
-        <v>720</v>
+        <v>714</v>
       </c>
       <c r="I165" s="7" t="s">
-        <v>730</v>
+        <v>724</v>
       </c>
     </row>
     <row r="166" spans="1:9" x14ac:dyDescent="0.4">
@@ -11613,7 +11613,7 @@
         <v>142</v>
       </c>
       <c r="I166" s="7" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
     </row>
     <row r="167" spans="1:9" x14ac:dyDescent="0.4">
@@ -11621,7 +11621,7 @@
         <v>143</v>
       </c>
       <c r="I167" s="7" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
     </row>
     <row r="168" spans="1:9" x14ac:dyDescent="0.4">
@@ -11629,7 +11629,7 @@
         <v>144</v>
       </c>
       <c r="I168" s="7" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
     </row>
     <row r="169" spans="1:9" x14ac:dyDescent="0.4">
@@ -11637,7 +11637,7 @@
         <v>145</v>
       </c>
       <c r="I169" s="7" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
     </row>
     <row r="170" spans="1:9" x14ac:dyDescent="0.4">
@@ -11645,7 +11645,7 @@
         <v>146</v>
       </c>
       <c r="I170" s="7" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
     </row>
     <row r="171" spans="1:9" x14ac:dyDescent="0.4">
@@ -11653,7 +11653,7 @@
         <v>147</v>
       </c>
       <c r="I171" s="7" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
     </row>
     <row r="172" spans="1:9" x14ac:dyDescent="0.4">
@@ -11661,7 +11661,7 @@
         <v>148</v>
       </c>
       <c r="I172" s="7" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
     </row>
     <row r="173" spans="1:9" x14ac:dyDescent="0.4">
@@ -11669,7 +11669,7 @@
         <v>149</v>
       </c>
       <c r="I173" s="7" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
     </row>
     <row r="174" spans="1:9" x14ac:dyDescent="0.4">
@@ -11677,7 +11677,7 @@
         <v>150</v>
       </c>
       <c r="I174" s="7" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
     </row>
     <row r="175" spans="1:9" x14ac:dyDescent="0.4">
@@ -11685,7 +11685,7 @@
         <v>151</v>
       </c>
       <c r="I175" s="7" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
     </row>
     <row r="176" spans="1:9" x14ac:dyDescent="0.4">
@@ -11693,7 +11693,7 @@
         <v>152</v>
       </c>
       <c r="I176" s="7" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
     </row>
     <row r="177" spans="1:9" x14ac:dyDescent="0.4">
@@ -11701,7 +11701,7 @@
         <v>153</v>
       </c>
       <c r="I177" s="7" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
     </row>
     <row r="178" spans="1:9" x14ac:dyDescent="0.4">
@@ -11709,7 +11709,7 @@
         <v>154</v>
       </c>
       <c r="I178" s="7" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
     </row>
     <row r="179" spans="1:9" x14ac:dyDescent="0.4">
@@ -11717,7 +11717,7 @@
         <v>155</v>
       </c>
       <c r="I179" s="7" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
     </row>
     <row r="180" spans="1:9" x14ac:dyDescent="0.4">
@@ -11725,7 +11725,7 @@
         <v>156</v>
       </c>
       <c r="I180" s="7" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
     </row>
     <row r="181" spans="1:9" x14ac:dyDescent="0.4">
@@ -11733,7 +11733,7 @@
         <v>157</v>
       </c>
       <c r="I181" s="7" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
     </row>
     <row r="182" spans="1:9" x14ac:dyDescent="0.4">
@@ -11741,7 +11741,7 @@
         <v>158</v>
       </c>
       <c r="I182" s="7" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
     </row>
     <row r="183" spans="1:9" x14ac:dyDescent="0.4">
@@ -11749,7 +11749,7 @@
         <v>159</v>
       </c>
       <c r="I183" s="7" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
     </row>
     <row r="184" spans="1:9" x14ac:dyDescent="0.4">
@@ -11757,7 +11757,7 @@
         <v>160</v>
       </c>
       <c r="I184" s="7" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
     </row>
     <row r="185" spans="1:9" x14ac:dyDescent="0.4">
@@ -11765,7 +11765,7 @@
         <v>161</v>
       </c>
       <c r="I185" s="7" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
     </row>
     <row r="186" spans="1:9" x14ac:dyDescent="0.4">
@@ -11773,7 +11773,7 @@
         <v>162</v>
       </c>
       <c r="I186" s="7" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
     </row>
     <row r="187" spans="1:9" x14ac:dyDescent="0.4">
@@ -11781,7 +11781,7 @@
         <v>163</v>
       </c>
       <c r="I187" s="7" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
     </row>
     <row r="188" spans="1:9" x14ac:dyDescent="0.4">
@@ -11789,7 +11789,7 @@
         <v>164</v>
       </c>
       <c r="I188" s="7" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
     </row>
     <row r="189" spans="1:9" x14ac:dyDescent="0.4">
@@ -11797,7 +11797,7 @@
         <v>165</v>
       </c>
       <c r="I189" s="7" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
     </row>
     <row r="190" spans="1:9" x14ac:dyDescent="0.4">
@@ -11805,7 +11805,7 @@
         <v>166</v>
       </c>
       <c r="I190" s="7" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
     </row>
     <row r="191" spans="1:9" x14ac:dyDescent="0.4">
@@ -11813,7 +11813,7 @@
         <v>167</v>
       </c>
       <c r="I191" s="7" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
     </row>
     <row r="192" spans="1:9" x14ac:dyDescent="0.4">
@@ -11821,7 +11821,7 @@
         <v>168</v>
       </c>
       <c r="I192" s="7" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
     </row>
     <row r="193" spans="1:9" x14ac:dyDescent="0.4">
@@ -11829,38 +11829,38 @@
         <v>169</v>
       </c>
       <c r="I193" s="7" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
     </row>
     <row r="194" spans="1:9" s="8" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B194" s="8" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="C194" s="8" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="D194" s="8" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="E194" s="8" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="F194" s="8" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="G194" s="8" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="H194" s="8" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
     </row>
     <row r="195" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A195" s="10" t="s">
-        <v>721</v>
+        <v>715</v>
       </c>
       <c r="I195" s="7" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
     </row>
     <row r="196" spans="1:9" x14ac:dyDescent="0.4">
@@ -11868,7 +11868,7 @@
         <v>170</v>
       </c>
       <c r="I196" s="7" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
     </row>
     <row r="197" spans="1:9" x14ac:dyDescent="0.4">
@@ -11876,7 +11876,7 @@
         <v>171</v>
       </c>
       <c r="I197" s="7" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
     </row>
     <row r="198" spans="1:9" x14ac:dyDescent="0.4">
@@ -11884,7 +11884,7 @@
         <v>172</v>
       </c>
       <c r="I198" s="7" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
     </row>
     <row r="199" spans="1:9" x14ac:dyDescent="0.4">
@@ -11892,7 +11892,7 @@
         <v>173</v>
       </c>
       <c r="I199" s="7" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
     </row>
     <row r="200" spans="1:9" x14ac:dyDescent="0.4">
@@ -11900,7 +11900,7 @@
         <v>174</v>
       </c>
       <c r="I200" s="7" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
     </row>
     <row r="201" spans="1:9" x14ac:dyDescent="0.4">
@@ -11908,7 +11908,7 @@
         <v>175</v>
       </c>
       <c r="I201" s="7" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
     </row>
     <row r="202" spans="1:9" x14ac:dyDescent="0.4">
@@ -11916,7 +11916,7 @@
         <v>176</v>
       </c>
       <c r="I202" s="7" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
     </row>
     <row r="203" spans="1:9" x14ac:dyDescent="0.4">
@@ -11924,7 +11924,7 @@
         <v>177</v>
       </c>
       <c r="I203" s="7" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
     </row>
     <row r="204" spans="1:9" x14ac:dyDescent="0.4">
@@ -11932,7 +11932,7 @@
         <v>178</v>
       </c>
       <c r="I204" s="7" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
     </row>
     <row r="205" spans="1:9" x14ac:dyDescent="0.4">
@@ -11940,7 +11940,7 @@
         <v>179</v>
       </c>
       <c r="I205" s="7" t="s">
-        <v>733</v>
+        <v>727</v>
       </c>
     </row>
     <row r="206" spans="1:9" x14ac:dyDescent="0.4">
@@ -11948,7 +11948,7 @@
         <v>180</v>
       </c>
       <c r="I206" s="7" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
     </row>
     <row r="207" spans="1:9" x14ac:dyDescent="0.4">
@@ -11956,7 +11956,7 @@
         <v>181</v>
       </c>
       <c r="I207" s="7" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
     </row>
     <row r="208" spans="1:9" x14ac:dyDescent="0.4">
@@ -11964,7 +11964,7 @@
         <v>182</v>
       </c>
       <c r="I208" s="7" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
     </row>
     <row r="209" spans="1:9" x14ac:dyDescent="0.4">
@@ -11972,7 +11972,7 @@
         <v>183</v>
       </c>
       <c r="I209" s="7" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
     </row>
     <row r="210" spans="1:9" x14ac:dyDescent="0.4">
@@ -11980,7 +11980,7 @@
         <v>184</v>
       </c>
       <c r="I210" s="7" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
     </row>
     <row r="211" spans="1:9" x14ac:dyDescent="0.4">
@@ -11988,7 +11988,7 @@
         <v>185</v>
       </c>
       <c r="I211" s="7" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
     </row>
     <row r="212" spans="1:9" x14ac:dyDescent="0.4">
@@ -11996,7 +11996,7 @@
         <v>186</v>
       </c>
       <c r="I212" s="7" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
     </row>
     <row r="213" spans="1:9" x14ac:dyDescent="0.4">
@@ -12004,7 +12004,7 @@
         <v>187</v>
       </c>
       <c r="I213" s="7" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
     </row>
     <row r="214" spans="1:9" x14ac:dyDescent="0.4">
@@ -12012,7 +12012,7 @@
         <v>188</v>
       </c>
       <c r="I214" s="7" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
     </row>
     <row r="215" spans="1:9" x14ac:dyDescent="0.4">
@@ -12020,7 +12020,7 @@
         <v>189</v>
       </c>
       <c r="I215" s="7" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
     </row>
     <row r="216" spans="1:9" x14ac:dyDescent="0.4">
@@ -12028,7 +12028,7 @@
         <v>190</v>
       </c>
       <c r="I216" s="7" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="217" spans="1:9" x14ac:dyDescent="0.4">
@@ -12036,7 +12036,7 @@
         <v>191</v>
       </c>
       <c r="I217" s="7" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
     </row>
     <row r="218" spans="1:9" x14ac:dyDescent="0.4">
@@ -12044,7 +12044,7 @@
         <v>192</v>
       </c>
       <c r="I218" s="7" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
     </row>
     <row r="219" spans="1:9" x14ac:dyDescent="0.4">
@@ -12052,7 +12052,7 @@
         <v>193</v>
       </c>
       <c r="I219" s="7" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
     </row>
     <row r="220" spans="1:9" x14ac:dyDescent="0.4">
@@ -12060,7 +12060,7 @@
         <v>194</v>
       </c>
       <c r="I220" s="7" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
     </row>
     <row r="221" spans="1:9" x14ac:dyDescent="0.4">
@@ -12068,7 +12068,7 @@
         <v>195</v>
       </c>
       <c r="I221" s="7" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
     </row>
     <row r="222" spans="1:9" x14ac:dyDescent="0.4">
@@ -12076,7 +12076,7 @@
         <v>196</v>
       </c>
       <c r="I222" s="7" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
     </row>
     <row r="223" spans="1:9" x14ac:dyDescent="0.4">
@@ -12084,7 +12084,7 @@
         <v>197</v>
       </c>
       <c r="I223" s="7" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
     </row>
     <row r="224" spans="1:9" x14ac:dyDescent="0.4">
@@ -12092,38 +12092,38 @@
         <v>198</v>
       </c>
       <c r="I224" s="7" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
     </row>
     <row r="225" spans="1:9" s="8" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B225" s="8" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="C225" s="8" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="D225" s="8" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="E225" s="8" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="F225" s="8" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="G225" s="8" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="H225" s="8" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
     </row>
     <row r="226" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A226" s="11" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="I226" s="7" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
     </row>
     <row r="227" spans="1:9" x14ac:dyDescent="0.4">
@@ -12131,7 +12131,7 @@
         <v>199</v>
       </c>
       <c r="I227" s="7" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
     </row>
     <row r="228" spans="1:9" x14ac:dyDescent="0.4">
@@ -12139,7 +12139,7 @@
         <v>200</v>
       </c>
       <c r="I228" s="7" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
     </row>
     <row r="229" spans="1:9" x14ac:dyDescent="0.4">
@@ -12147,7 +12147,7 @@
         <v>201</v>
       </c>
       <c r="I229" s="7" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
     </row>
     <row r="230" spans="1:9" x14ac:dyDescent="0.4">
@@ -12155,7 +12155,7 @@
         <v>202</v>
       </c>
       <c r="I230" s="7" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
     </row>
     <row r="231" spans="1:9" x14ac:dyDescent="0.4">
@@ -12163,7 +12163,7 @@
         <v>203</v>
       </c>
       <c r="I231" s="7" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
     </row>
     <row r="232" spans="1:9" x14ac:dyDescent="0.4">
@@ -12171,7 +12171,7 @@
         <v>204</v>
       </c>
       <c r="I232" s="7" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
     </row>
     <row r="233" spans="1:9" x14ac:dyDescent="0.4">
@@ -12179,7 +12179,7 @@
         <v>205</v>
       </c>
       <c r="I233" s="7" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
     </row>
     <row r="234" spans="1:9" x14ac:dyDescent="0.4">
@@ -12187,7 +12187,7 @@
         <v>206</v>
       </c>
       <c r="I234" s="7" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
     </row>
     <row r="235" spans="1:9" x14ac:dyDescent="0.4">
@@ -12195,7 +12195,7 @@
         <v>207</v>
       </c>
       <c r="I235" s="7" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
     </row>
     <row r="236" spans="1:9" x14ac:dyDescent="0.4">
@@ -12203,7 +12203,7 @@
         <v>208</v>
       </c>
       <c r="I236" s="7" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
     </row>
     <row r="237" spans="1:9" x14ac:dyDescent="0.4">
@@ -12211,7 +12211,7 @@
         <v>209</v>
       </c>
       <c r="I237" s="7" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
     </row>
     <row r="238" spans="1:9" x14ac:dyDescent="0.4">
@@ -12219,7 +12219,7 @@
         <v>210</v>
       </c>
       <c r="I238" s="7" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
     </row>
     <row r="239" spans="1:9" x14ac:dyDescent="0.4">
@@ -12227,7 +12227,7 @@
         <v>211</v>
       </c>
       <c r="I239" s="7" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
     </row>
     <row r="240" spans="1:9" x14ac:dyDescent="0.4">
@@ -12235,7 +12235,7 @@
         <v>212</v>
       </c>
       <c r="I240" s="7" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
     </row>
     <row r="241" spans="1:9" x14ac:dyDescent="0.4">
@@ -12243,7 +12243,7 @@
         <v>213</v>
       </c>
       <c r="I241" s="7" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
     </row>
     <row r="242" spans="1:9" x14ac:dyDescent="0.4">
@@ -12251,7 +12251,7 @@
         <v>214</v>
       </c>
       <c r="I242" s="7" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
     </row>
     <row r="243" spans="1:9" x14ac:dyDescent="0.4">
@@ -12259,7 +12259,7 @@
         <v>215</v>
       </c>
       <c r="I243" s="7" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
     </row>
     <row r="244" spans="1:9" x14ac:dyDescent="0.4">
@@ -12267,7 +12267,7 @@
         <v>216</v>
       </c>
       <c r="I244" s="7" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
     </row>
     <row r="245" spans="1:9" x14ac:dyDescent="0.4">
@@ -12275,7 +12275,7 @@
         <v>217</v>
       </c>
       <c r="I245" s="7" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
     </row>
     <row r="246" spans="1:9" x14ac:dyDescent="0.4">
@@ -12283,7 +12283,7 @@
         <v>218</v>
       </c>
       <c r="I246" s="7" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
     </row>
     <row r="247" spans="1:9" x14ac:dyDescent="0.4">
@@ -12291,7 +12291,7 @@
         <v>219</v>
       </c>
       <c r="I247" s="7" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
     </row>
     <row r="248" spans="1:9" x14ac:dyDescent="0.4">
@@ -12299,7 +12299,7 @@
         <v>220</v>
       </c>
       <c r="I248" s="7" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
     </row>
     <row r="249" spans="1:9" x14ac:dyDescent="0.4">
@@ -12307,7 +12307,7 @@
         <v>221</v>
       </c>
       <c r="I249" s="7" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
     </row>
     <row r="250" spans="1:9" x14ac:dyDescent="0.4">
@@ -12315,7 +12315,7 @@
         <v>222</v>
       </c>
       <c r="I250" s="7" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
     </row>
     <row r="251" spans="1:9" x14ac:dyDescent="0.4">
@@ -12323,7 +12323,7 @@
         <v>223</v>
       </c>
       <c r="I251" s="7" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
     </row>
     <row r="252" spans="1:9" x14ac:dyDescent="0.4">
@@ -12331,7 +12331,7 @@
         <v>224</v>
       </c>
       <c r="I252" s="7" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
     </row>
     <row r="253" spans="1:9" x14ac:dyDescent="0.4">
@@ -12339,7 +12339,7 @@
         <v>225</v>
       </c>
       <c r="I253" s="7" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
     </row>
     <row r="254" spans="1:9" x14ac:dyDescent="0.4">
@@ -12347,7 +12347,7 @@
         <v>226</v>
       </c>
       <c r="I254" s="7" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
     </row>
     <row r="255" spans="1:9" x14ac:dyDescent="0.4">
@@ -12355,38 +12355,38 @@
         <v>227</v>
       </c>
       <c r="I255" s="7" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
     </row>
     <row r="256" spans="1:9" s="8" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B256" s="8" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="C256" s="8" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="D256" s="8" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="E256" s="8" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="F256" s="8" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="G256" s="8" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="H256" s="8" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
     </row>
     <row r="257" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A257" s="6" t="s">
-        <v>723</v>
+        <v>717</v>
       </c>
       <c r="I257" s="7" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
     </row>
     <row r="258" spans="1:9" x14ac:dyDescent="0.4">
@@ -12394,7 +12394,7 @@
         <v>228</v>
       </c>
       <c r="I258" s="7" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
     </row>
     <row r="259" spans="1:9" x14ac:dyDescent="0.4">
@@ -12402,7 +12402,7 @@
         <v>229</v>
       </c>
       <c r="I259" s="7" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
     </row>
     <row r="260" spans="1:9" x14ac:dyDescent="0.4">
@@ -12410,7 +12410,7 @@
         <v>230</v>
       </c>
       <c r="I260" s="7" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
     </row>
     <row r="261" spans="1:9" x14ac:dyDescent="0.4">
@@ -12418,7 +12418,7 @@
         <v>231</v>
       </c>
       <c r="I261" s="7" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
     </row>
     <row r="262" spans="1:9" x14ac:dyDescent="0.4">
@@ -12426,7 +12426,7 @@
         <v>232</v>
       </c>
       <c r="I262" s="7" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
     </row>
     <row r="263" spans="1:9" x14ac:dyDescent="0.4">
@@ -12434,7 +12434,7 @@
         <v>233</v>
       </c>
       <c r="I263" s="7" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
     </row>
     <row r="264" spans="1:9" x14ac:dyDescent="0.4">
@@ -12442,7 +12442,7 @@
         <v>234</v>
       </c>
       <c r="I264" s="7" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
     </row>
     <row r="265" spans="1:9" x14ac:dyDescent="0.4">
@@ -12450,7 +12450,7 @@
         <v>235</v>
       </c>
       <c r="I265" s="7" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
     </row>
     <row r="266" spans="1:9" x14ac:dyDescent="0.4">
@@ -12458,7 +12458,7 @@
         <v>236</v>
       </c>
       <c r="I266" s="7" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
     </row>
     <row r="267" spans="1:9" x14ac:dyDescent="0.4">
@@ -12466,7 +12466,7 @@
         <v>237</v>
       </c>
       <c r="I267" s="7" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
     </row>
     <row r="268" spans="1:9" x14ac:dyDescent="0.4">
@@ -12474,7 +12474,7 @@
         <v>238</v>
       </c>
       <c r="I268" s="7" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
     </row>
     <row r="269" spans="1:9" x14ac:dyDescent="0.4">
@@ -12482,7 +12482,7 @@
         <v>239</v>
       </c>
       <c r="I269" s="7" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
     </row>
     <row r="270" spans="1:9" x14ac:dyDescent="0.4">
@@ -12490,7 +12490,7 @@
         <v>240</v>
       </c>
       <c r="I270" s="7" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
     </row>
     <row r="271" spans="1:9" x14ac:dyDescent="0.4">
@@ -12498,7 +12498,7 @@
         <v>241</v>
       </c>
       <c r="I271" s="7" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
     </row>
     <row r="272" spans="1:9" x14ac:dyDescent="0.4">
@@ -12506,7 +12506,7 @@
         <v>242</v>
       </c>
       <c r="I272" s="7" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
     </row>
     <row r="273" spans="1:9" x14ac:dyDescent="0.4">
@@ -12514,7 +12514,7 @@
         <v>243</v>
       </c>
       <c r="I273" s="7" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
     </row>
     <row r="274" spans="1:9" x14ac:dyDescent="0.4">
@@ -12522,7 +12522,7 @@
         <v>244</v>
       </c>
       <c r="I274" s="7" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
     </row>
     <row r="275" spans="1:9" x14ac:dyDescent="0.4">
@@ -12530,7 +12530,7 @@
         <v>245</v>
       </c>
       <c r="I275" s="7" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
     </row>
     <row r="276" spans="1:9" x14ac:dyDescent="0.4">
@@ -12538,7 +12538,7 @@
         <v>246</v>
       </c>
       <c r="I276" s="7" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
     </row>
     <row r="277" spans="1:9" x14ac:dyDescent="0.4">
@@ -12546,7 +12546,7 @@
         <v>247</v>
       </c>
       <c r="I277" s="7" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
     </row>
     <row r="278" spans="1:9" x14ac:dyDescent="0.4">
@@ -12554,7 +12554,7 @@
         <v>248</v>
       </c>
       <c r="I278" s="7" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
     </row>
     <row r="279" spans="1:9" x14ac:dyDescent="0.4">
@@ -12562,7 +12562,7 @@
         <v>249</v>
       </c>
       <c r="I279" s="7" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
     </row>
     <row r="280" spans="1:9" x14ac:dyDescent="0.4">
@@ -12570,7 +12570,7 @@
         <v>250</v>
       </c>
       <c r="I280" s="7" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
     </row>
     <row r="281" spans="1:9" x14ac:dyDescent="0.4">
@@ -12578,7 +12578,7 @@
         <v>251</v>
       </c>
       <c r="I281" s="7" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
     </row>
     <row r="282" spans="1:9" x14ac:dyDescent="0.4">
@@ -12586,7 +12586,7 @@
         <v>252</v>
       </c>
       <c r="I282" s="7" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="283" spans="1:9" x14ac:dyDescent="0.4">
@@ -12594,7 +12594,7 @@
         <v>253</v>
       </c>
       <c r="I283" s="7" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
     </row>
     <row r="284" spans="1:9" x14ac:dyDescent="0.4">
@@ -12602,7 +12602,7 @@
         <v>254</v>
       </c>
       <c r="I284" s="7" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
     </row>
     <row r="285" spans="1:9" x14ac:dyDescent="0.4">
@@ -12610,7 +12610,7 @@
         <v>255</v>
       </c>
       <c r="I285" s="7" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
     </row>
     <row r="286" spans="1:9" x14ac:dyDescent="0.4">
@@ -12618,38 +12618,38 @@
         <v>256</v>
       </c>
       <c r="I286" s="7" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
     </row>
     <row r="287" spans="1:9" s="8" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B287" s="8" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="C287" s="8" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="D287" s="8" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="E287" s="8" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="F287" s="8" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="G287" s="8" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="H287" s="8" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
     </row>
     <row r="288" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A288" s="9" t="s">
-        <v>724</v>
+        <v>718</v>
       </c>
       <c r="I288" s="7" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
     </row>
     <row r="289" spans="1:9" x14ac:dyDescent="0.4">
@@ -12657,7 +12657,7 @@
         <v>257</v>
       </c>
       <c r="I289" s="7" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
     </row>
     <row r="290" spans="1:9" x14ac:dyDescent="0.4">
@@ -12665,7 +12665,7 @@
         <v>258</v>
       </c>
       <c r="I290" s="7" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
     </row>
     <row r="291" spans="1:9" x14ac:dyDescent="0.4">
@@ -12673,7 +12673,7 @@
         <v>259</v>
       </c>
       <c r="I291" s="7" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="292" spans="1:9" x14ac:dyDescent="0.4">
@@ -12681,7 +12681,7 @@
         <v>260</v>
       </c>
       <c r="I292" s="7" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
     </row>
     <row r="293" spans="1:9" x14ac:dyDescent="0.4">
@@ -12689,7 +12689,7 @@
         <v>261</v>
       </c>
       <c r="I293" s="7" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
     </row>
     <row r="294" spans="1:9" x14ac:dyDescent="0.4">
@@ -12697,7 +12697,7 @@
         <v>262</v>
       </c>
       <c r="I294" s="7" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
     </row>
     <row r="295" spans="1:9" x14ac:dyDescent="0.4">
@@ -12705,7 +12705,7 @@
         <v>263</v>
       </c>
       <c r="I295" s="7" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
     </row>
     <row r="296" spans="1:9" x14ac:dyDescent="0.4">
@@ -12713,7 +12713,7 @@
         <v>264</v>
       </c>
       <c r="I296" s="7" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
     </row>
     <row r="297" spans="1:9" x14ac:dyDescent="0.4">
@@ -12721,7 +12721,7 @@
         <v>265</v>
       </c>
       <c r="I297" s="7" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
     </row>
     <row r="298" spans="1:9" x14ac:dyDescent="0.4">
@@ -12729,7 +12729,7 @@
         <v>266</v>
       </c>
       <c r="I298" s="7" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
     </row>
     <row r="299" spans="1:9" x14ac:dyDescent="0.4">
@@ -12737,7 +12737,7 @@
         <v>267</v>
       </c>
       <c r="I299" s="7" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
     </row>
     <row r="300" spans="1:9" x14ac:dyDescent="0.4">
@@ -12745,7 +12745,7 @@
         <v>268</v>
       </c>
       <c r="I300" s="7" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
     </row>
     <row r="301" spans="1:9" x14ac:dyDescent="0.4">
@@ -12753,7 +12753,7 @@
         <v>269</v>
       </c>
       <c r="I301" s="7" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
     </row>
     <row r="302" spans="1:9" x14ac:dyDescent="0.4">
@@ -12761,7 +12761,7 @@
         <v>270</v>
       </c>
       <c r="I302" s="7" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
     </row>
     <row r="303" spans="1:9" x14ac:dyDescent="0.4">
@@ -12769,7 +12769,7 @@
         <v>271</v>
       </c>
       <c r="I303" s="7" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
     </row>
     <row r="304" spans="1:9" x14ac:dyDescent="0.4">
@@ -12777,7 +12777,7 @@
         <v>272</v>
       </c>
       <c r="I304" s="7" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
     </row>
     <row r="305" spans="1:9" x14ac:dyDescent="0.4">
@@ -12785,7 +12785,7 @@
         <v>273</v>
       </c>
       <c r="I305" s="7" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
     </row>
     <row r="306" spans="1:9" x14ac:dyDescent="0.4">
@@ -12793,7 +12793,7 @@
         <v>274</v>
       </c>
       <c r="I306" s="7" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
     </row>
     <row r="307" spans="1:9" x14ac:dyDescent="0.4">
@@ -12801,7 +12801,7 @@
         <v>275</v>
       </c>
       <c r="I307" s="7" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
     </row>
     <row r="308" spans="1:9" x14ac:dyDescent="0.4">
@@ -12809,7 +12809,7 @@
         <v>276</v>
       </c>
       <c r="I308" s="7" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
     </row>
     <row r="309" spans="1:9" x14ac:dyDescent="0.4">
@@ -12817,7 +12817,7 @@
         <v>277</v>
       </c>
       <c r="I309" s="7" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
     </row>
     <row r="310" spans="1:9" x14ac:dyDescent="0.4">
@@ -12825,7 +12825,7 @@
         <v>278</v>
       </c>
       <c r="I310" s="7" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
     </row>
     <row r="311" spans="1:9" x14ac:dyDescent="0.4">
@@ -12833,7 +12833,7 @@
         <v>279</v>
       </c>
       <c r="I311" s="7" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
     </row>
     <row r="312" spans="1:9" x14ac:dyDescent="0.4">
@@ -12841,7 +12841,7 @@
         <v>280</v>
       </c>
       <c r="I312" s="7" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
     </row>
     <row r="313" spans="1:9" x14ac:dyDescent="0.4">
@@ -12849,7 +12849,7 @@
         <v>281</v>
       </c>
       <c r="I313" s="7" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
     </row>
     <row r="314" spans="1:9" x14ac:dyDescent="0.4">
@@ -12857,7 +12857,7 @@
         <v>282</v>
       </c>
       <c r="I314" s="7" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
     </row>
     <row r="315" spans="1:9" x14ac:dyDescent="0.4">
@@ -12865,7 +12865,7 @@
         <v>283</v>
       </c>
       <c r="I315" s="7" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
     </row>
     <row r="316" spans="1:9" x14ac:dyDescent="0.4">
@@ -12873,7 +12873,7 @@
         <v>284</v>
       </c>
       <c r="I316" s="7" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
     </row>
     <row r="317" spans="1:9" x14ac:dyDescent="0.4">
@@ -12881,38 +12881,38 @@
         <v>285</v>
       </c>
       <c r="I317" s="7" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
     </row>
     <row r="318" spans="1:9" s="8" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B318" s="8" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="C318" s="8" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="D318" s="8" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="E318" s="8" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="F318" s="8" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="G318" s="8" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="H318" s="8" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
     </row>
     <row r="319" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A319" s="10" t="s">
-        <v>725</v>
+        <v>719</v>
       </c>
       <c r="I319" s="7" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
     </row>
     <row r="320" spans="1:9" x14ac:dyDescent="0.4">
@@ -12920,7 +12920,7 @@
         <v>286</v>
       </c>
       <c r="I320" s="7" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
     </row>
     <row r="321" spans="1:9" x14ac:dyDescent="0.4">
@@ -12928,7 +12928,7 @@
         <v>287</v>
       </c>
       <c r="I321" s="7" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
     </row>
     <row r="322" spans="1:9" x14ac:dyDescent="0.4">
@@ -12936,7 +12936,7 @@
         <v>288</v>
       </c>
       <c r="I322" s="7" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
     </row>
     <row r="323" spans="1:9" x14ac:dyDescent="0.4">
@@ -12944,7 +12944,7 @@
         <v>289</v>
       </c>
       <c r="I323" s="7" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
     </row>
     <row r="324" spans="1:9" x14ac:dyDescent="0.4">
@@ -12952,7 +12952,7 @@
         <v>290</v>
       </c>
       <c r="I324" s="7" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
     </row>
     <row r="325" spans="1:9" x14ac:dyDescent="0.4">
@@ -12960,7 +12960,7 @@
         <v>291</v>
       </c>
       <c r="I325" s="7" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
     </row>
     <row r="326" spans="1:9" x14ac:dyDescent="0.4">
@@ -12968,7 +12968,7 @@
         <v>292</v>
       </c>
       <c r="I326" s="7" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
     </row>
     <row r="327" spans="1:9" x14ac:dyDescent="0.4">
@@ -12976,7 +12976,7 @@
         <v>293</v>
       </c>
       <c r="I327" s="7" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
     </row>
     <row r="328" spans="1:9" x14ac:dyDescent="0.4">
@@ -12984,7 +12984,7 @@
         <v>294</v>
       </c>
       <c r="I328" s="7" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
     </row>
     <row r="329" spans="1:9" x14ac:dyDescent="0.4">
@@ -12992,7 +12992,7 @@
         <v>295</v>
       </c>
       <c r="I329" s="7" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
     </row>
     <row r="330" spans="1:9" x14ac:dyDescent="0.4">
@@ -13000,7 +13000,7 @@
         <v>296</v>
       </c>
       <c r="I330" s="7" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
     </row>
     <row r="331" spans="1:9" x14ac:dyDescent="0.4">
@@ -13008,7 +13008,7 @@
         <v>297</v>
       </c>
       <c r="I331" s="7" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
     </row>
     <row r="332" spans="1:9" x14ac:dyDescent="0.4">
@@ -13016,7 +13016,7 @@
         <v>298</v>
       </c>
       <c r="I332" s="7" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
     </row>
     <row r="333" spans="1:9" x14ac:dyDescent="0.4">
@@ -13024,7 +13024,7 @@
         <v>299</v>
       </c>
       <c r="I333" s="7" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
     </row>
     <row r="334" spans="1:9" x14ac:dyDescent="0.4">
@@ -13032,7 +13032,7 @@
         <v>300</v>
       </c>
       <c r="I334" s="7" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
     </row>
     <row r="335" spans="1:9" x14ac:dyDescent="0.4">
@@ -13040,7 +13040,7 @@
         <v>301</v>
       </c>
       <c r="I335" s="7" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
     </row>
     <row r="336" spans="1:9" x14ac:dyDescent="0.4">
@@ -13048,7 +13048,7 @@
         <v>302</v>
       </c>
       <c r="I336" s="7" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
     </row>
     <row r="337" spans="1:9" x14ac:dyDescent="0.4">
@@ -13056,7 +13056,7 @@
         <v>303</v>
       </c>
       <c r="I337" s="7" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
     </row>
     <row r="338" spans="1:9" x14ac:dyDescent="0.4">
@@ -13064,7 +13064,7 @@
         <v>304</v>
       </c>
       <c r="I338" s="7" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
     </row>
     <row r="339" spans="1:9" x14ac:dyDescent="0.4">
@@ -13072,7 +13072,7 @@
         <v>305</v>
       </c>
       <c r="I339" s="7" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
     </row>
     <row r="340" spans="1:9" x14ac:dyDescent="0.4">
@@ -13080,7 +13080,7 @@
         <v>306</v>
       </c>
       <c r="I340" s="7" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
     </row>
     <row r="341" spans="1:9" x14ac:dyDescent="0.4">
@@ -13088,7 +13088,7 @@
         <v>307</v>
       </c>
       <c r="I341" s="7" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
     </row>
     <row r="342" spans="1:9" x14ac:dyDescent="0.4">
@@ -13096,7 +13096,7 @@
         <v>308</v>
       </c>
       <c r="I342" s="7" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
     </row>
     <row r="343" spans="1:9" x14ac:dyDescent="0.4">
@@ -13104,7 +13104,7 @@
         <v>309</v>
       </c>
       <c r="I343" s="7" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
     </row>
     <row r="344" spans="1:9" x14ac:dyDescent="0.4">
@@ -13112,7 +13112,7 @@
         <v>310</v>
       </c>
       <c r="I344" s="7" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
     </row>
     <row r="345" spans="1:9" x14ac:dyDescent="0.4">
@@ -13120,7 +13120,7 @@
         <v>311</v>
       </c>
       <c r="I345" s="7" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
     </row>
     <row r="346" spans="1:9" x14ac:dyDescent="0.4">
@@ -13128,7 +13128,7 @@
         <v>312</v>
       </c>
       <c r="I346" s="7" t="s">
-        <v>666</v>
+        <v>729</v>
       </c>
     </row>
     <row r="347" spans="1:9" x14ac:dyDescent="0.4">
@@ -13136,7 +13136,7 @@
         <v>313</v>
       </c>
       <c r="I347" s="7" t="s">
-        <v>667</v>
+        <v>663</v>
       </c>
     </row>
     <row r="348" spans="1:9" x14ac:dyDescent="0.4">
@@ -13144,38 +13144,38 @@
         <v>314</v>
       </c>
       <c r="I348" s="7" t="s">
-        <v>668</v>
+        <v>664</v>
       </c>
     </row>
     <row r="349" spans="1:9" s="8" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B349" s="8" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="C349" s="8" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="D349" s="8" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="E349" s="8" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="F349" s="8" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="G349" s="8" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="H349" s="8" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
     </row>
     <row r="350" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A350" s="11" t="s">
-        <v>726</v>
+        <v>720</v>
       </c>
       <c r="I350" s="7" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
     </row>
     <row r="351" spans="1:9" x14ac:dyDescent="0.4">
@@ -13183,7 +13183,7 @@
         <v>315</v>
       </c>
       <c r="I351" s="7" t="s">
-        <v>670</v>
+        <v>666</v>
       </c>
     </row>
     <row r="352" spans="1:9" x14ac:dyDescent="0.4">
@@ -13191,7 +13191,7 @@
         <v>316</v>
       </c>
       <c r="I352" s="7" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
     </row>
     <row r="353" spans="1:9" x14ac:dyDescent="0.4">
@@ -13199,7 +13199,7 @@
         <v>317</v>
       </c>
       <c r="I353" s="7" t="s">
-        <v>672</v>
+        <v>668</v>
       </c>
     </row>
     <row r="354" spans="1:9" x14ac:dyDescent="0.4">
@@ -13207,7 +13207,7 @@
         <v>318</v>
       </c>
       <c r="I354" s="7" t="s">
-        <v>673</v>
+        <v>669</v>
       </c>
     </row>
     <row r="355" spans="1:9" x14ac:dyDescent="0.4">
@@ -13215,7 +13215,7 @@
         <v>319</v>
       </c>
       <c r="I355" s="7" t="s">
-        <v>674</v>
+        <v>670</v>
       </c>
     </row>
     <row r="356" spans="1:9" x14ac:dyDescent="0.4">
@@ -13223,7 +13223,7 @@
         <v>320</v>
       </c>
       <c r="I356" s="7" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
     </row>
     <row r="357" spans="1:9" x14ac:dyDescent="0.4">
@@ -13231,7 +13231,7 @@
         <v>321</v>
       </c>
       <c r="I357" s="7" t="s">
-        <v>676</v>
+        <v>672</v>
       </c>
     </row>
     <row r="358" spans="1:9" x14ac:dyDescent="0.4">
@@ -13239,7 +13239,7 @@
         <v>322</v>
       </c>
       <c r="I358" s="7" t="s">
-        <v>677</v>
+        <v>673</v>
       </c>
     </row>
     <row r="359" spans="1:9" x14ac:dyDescent="0.4">
@@ -13247,7 +13247,7 @@
         <v>323</v>
       </c>
       <c r="I359" s="7" t="s">
-        <v>678</v>
+        <v>674</v>
       </c>
     </row>
     <row r="360" spans="1:9" x14ac:dyDescent="0.4">
@@ -13255,7 +13255,7 @@
         <v>324</v>
       </c>
       <c r="I360" s="7" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
     </row>
     <row r="361" spans="1:9" x14ac:dyDescent="0.4">
@@ -13263,7 +13263,7 @@
         <v>325</v>
       </c>
       <c r="I361" s="7" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
     </row>
     <row r="362" spans="1:9" x14ac:dyDescent="0.4">
@@ -13271,7 +13271,7 @@
         <v>326</v>
       </c>
       <c r="I362" s="7" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
     </row>
     <row r="363" spans="1:9" x14ac:dyDescent="0.4">
@@ -13279,7 +13279,7 @@
         <v>327</v>
       </c>
       <c r="I363" s="7" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
     </row>
     <row r="364" spans="1:9" x14ac:dyDescent="0.4">
@@ -13287,7 +13287,7 @@
         <v>328</v>
       </c>
       <c r="I364" s="7" t="s">
-        <v>683</v>
+        <v>679</v>
       </c>
     </row>
     <row r="365" spans="1:9" x14ac:dyDescent="0.4">
@@ -13295,7 +13295,7 @@
         <v>329</v>
       </c>
       <c r="I365" s="7" t="s">
-        <v>684</v>
+        <v>680</v>
       </c>
     </row>
     <row r="366" spans="1:9" x14ac:dyDescent="0.4">
@@ -13303,7 +13303,7 @@
         <v>330</v>
       </c>
       <c r="I366" s="7" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
     </row>
     <row r="367" spans="1:9" x14ac:dyDescent="0.4">
@@ -13311,7 +13311,7 @@
         <v>331</v>
       </c>
       <c r="I367" s="7" t="s">
-        <v>686</v>
+        <v>728</v>
       </c>
     </row>
     <row r="368" spans="1:9" x14ac:dyDescent="0.4">
@@ -13319,7 +13319,7 @@
         <v>332</v>
       </c>
       <c r="I368" s="7" t="s">
-        <v>687</v>
+        <v>682</v>
       </c>
     </row>
     <row r="369" spans="1:9" x14ac:dyDescent="0.4">
@@ -13327,7 +13327,7 @@
         <v>333</v>
       </c>
       <c r="I369" s="7" t="s">
-        <v>688</v>
+        <v>683</v>
       </c>
     </row>
     <row r="370" spans="1:9" x14ac:dyDescent="0.4">
@@ -13335,7 +13335,7 @@
         <v>334</v>
       </c>
       <c r="I370" s="7" t="s">
-        <v>689</v>
+        <v>684</v>
       </c>
     </row>
     <row r="371" spans="1:9" x14ac:dyDescent="0.4">
@@ -13343,7 +13343,7 @@
         <v>335</v>
       </c>
       <c r="I371" s="7" t="s">
-        <v>690</v>
+        <v>685</v>
       </c>
     </row>
     <row r="372" spans="1:9" x14ac:dyDescent="0.4">
@@ -13351,7 +13351,7 @@
         <v>336</v>
       </c>
       <c r="I372" s="7" t="s">
-        <v>691</v>
+        <v>686</v>
       </c>
     </row>
     <row r="373" spans="1:9" x14ac:dyDescent="0.4">
@@ -13359,7 +13359,7 @@
         <v>337</v>
       </c>
       <c r="I373" s="7" t="s">
-        <v>692</v>
+        <v>733</v>
       </c>
     </row>
     <row r="374" spans="1:9" x14ac:dyDescent="0.4">
@@ -13367,7 +13367,7 @@
         <v>338</v>
       </c>
       <c r="I374" s="7" t="s">
-        <v>693</v>
+        <v>687</v>
       </c>
     </row>
     <row r="375" spans="1:9" x14ac:dyDescent="0.4">
@@ -13375,7 +13375,7 @@
         <v>339</v>
       </c>
       <c r="I375" s="7" t="s">
-        <v>694</v>
+        <v>688</v>
       </c>
     </row>
     <row r="376" spans="1:9" x14ac:dyDescent="0.4">
@@ -13383,7 +13383,7 @@
         <v>340</v>
       </c>
       <c r="I376" s="7" t="s">
-        <v>695</v>
+        <v>689</v>
       </c>
     </row>
     <row r="377" spans="1:9" x14ac:dyDescent="0.4">
@@ -13391,7 +13391,7 @@
         <v>341</v>
       </c>
       <c r="I377" s="7" t="s">
-        <v>696</v>
+        <v>690</v>
       </c>
     </row>
     <row r="378" spans="1:9" x14ac:dyDescent="0.4">
@@ -13399,7 +13399,7 @@
         <v>342</v>
       </c>
       <c r="I378" s="7" t="s">
-        <v>697</v>
+        <v>691</v>
       </c>
     </row>
     <row r="379" spans="1:9" x14ac:dyDescent="0.4">
@@ -13407,36 +13407,36 @@
         <v>343</v>
       </c>
       <c r="I379" s="7" t="s">
-        <v>698</v>
+        <v>692</v>
       </c>
     </row>
     <row r="380" spans="1:9" s="8" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A380" s="8" t="s">
-        <v>727</v>
+        <v>721</v>
       </c>
       <c r="B380" s="8" t="s">
-        <v>727</v>
+        <v>721</v>
       </c>
       <c r="C380" s="8" t="s">
-        <v>727</v>
+        <v>721</v>
       </c>
       <c r="D380" s="8" t="s">
-        <v>727</v>
+        <v>721</v>
       </c>
       <c r="E380" s="8" t="s">
-        <v>727</v>
+        <v>721</v>
       </c>
       <c r="F380" s="8" t="s">
-        <v>727</v>
+        <v>721</v>
       </c>
       <c r="G380" s="8" t="s">
-        <v>727</v>
+        <v>721</v>
       </c>
       <c r="H380" s="8" t="s">
-        <v>727</v>
+        <v>721</v>
       </c>
       <c r="I380" s="8" t="s">
-        <v>727</v>
+        <v>721</v>
       </c>
     </row>
   </sheetData>
